--- a/assessment_forms/041_healthcare_compliance_skills_quiz--assessment_forms.xlsx
+++ b/assessment_forms/041_healthcare_compliance_skills_quiz--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>training_checkin_1</t>
+          <t>training_frequency</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Staff Training Check-in</t>
+          <t>How often do you receive regular training on healthcare compliance?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>training_checkin_2</t>
+          <t>policy_understanding</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Training Frequency</t>
+          <t>What is your level of understanding of healthcare policies?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>training_checkin_3</t>
+          <t>training_checkin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Policy Understanding</t>
+          <t>Do you regularly check in with training providers?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>compliance_quiz_1</t>
+          <t>compliance_status</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Compliance Quiz</t>
+          <t>What is your compliance status?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,35 +612,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>compliance_quiz_2</t>
+          <t>training_sessions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Compliance Score</t>
+          <t>How many training sessions do you have within the past 6 months?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>training_checkin_4</t>
+          <t>training_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Training Check-in</t>
+          <t>What is the date of your most recent training session?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>training_checkin_5</t>
+          <t>training_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Training Status</t>
+          <t>How many hours do you typically spend on training per week?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>training_checkin_6</t>
+          <t>training_topics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Training Date</t>
+          <t>Which training topics do you have received recently?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>training_checkin_7</t>
+          <t>training_provider</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Training Time</t>
+          <t>What is the name of your most recent training provider?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>training_checkin_8</t>
+          <t>compliance_score</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Training Location</t>
+          <t>What is your current compliance score?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>training_checkin_9</t>
+          <t>training_status</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Training Topic</t>
+          <t>Do you have active or inactive training status?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>training_checkin_10</t>
+          <t>next_session_date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Training Provider</t>
+          <t>What is the date of your next training session?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>training_checkin_11</t>
+          <t>next_session_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Compliance Score</t>
+          <t>What time is your next training session?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>training_checkin_12</t>
+          <t>next_session_location</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Training Status</t>
+          <t>Where is the location of your next training session?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>training_checkin_13</t>
+          <t>next_session_topic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Training Date</t>
+          <t>What is the topic of your next training session?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>training_checkin_14</t>
+          <t>next_session_provider</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Training Time</t>
+          <t>Who is your next training provider?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>training_checkin_15</t>
+          <t>next_session_hours</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Training Location</t>
+          <t>How many hours will you spend on the next training session?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>training_checkin_16</t>
+          <t>next_session_status</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Training Topic</t>
+          <t>What is the status of your next training session?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -937,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -965,170 +965,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>compliance_quiz_1_choices</t>
+          <t>training_frequency_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>compliance_quiz_1_choices</t>
+          <t>training_frequency_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training_checkin_5_choices</t>
+          <t>training_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>training_checkin_5_choices</t>
+          <t>training_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>training_checkin_9_choices</t>
+          <t>compliance_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>training_checkin_9_choices</t>
+          <t>compliance_status_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>training_checkin_12_choices</t>
+          <t>training_topics_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>compliance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Compliance</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>training_checkin_12_choices</t>
+          <t>training_topics_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>clinical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Clinical</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>training_checkin_16_choices</t>
+          <t>training_topics_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>administrative</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Administrative</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>training_checkin_16_choices</t>
+          <t>training_topics_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>training_status_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>training_status_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>next_session_topic_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>compliance</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>next_session_topic_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>clinical</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Clinical</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>next_session_topic_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>administrative</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Administrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>next_session_topic_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>next_session_status_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>next_session_status_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>inactive</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
